--- a/stories/arbres/TREE-VIV-005.xlsx
+++ b/stories/arbres/TREE-VIV-005.xlsx
@@ -489,7 +489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -831,6 +831,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -845,7 +857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV87"/>
+  <dimension ref="A1:AW87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1139,6 +1151,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1163,7 +1180,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Hugo est au parc, près de la ferme, avec maman. Un coq chante. Une poule picore. Un poussin suit. Maman dit : trois noms de la famille. Coq, poule, poussin. Hugo répète.</t>
+          <t>Hugo est au parc, près de la ferme, avec maman. Un coq chante. Une poule picore. Un poussin suit. Trois noms de la famille. Coq, poule, poussin. Hugo répète.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1301,6 +1318,13 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo est au parc, près de la ferme, avec maman. Un coq chante. Une poule picore. Un poussin suit.
+maman|Trois noms de la famille. Coq, poule, poussin.
+narrateur|Hugo répète.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1487,6 +1511,11 @@
         <v>8</v>
       </c>
       <c r="AV3" s="2" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le poulailler, le pré, ou la niche.</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1649,6 +1678,11 @@
         <v>8</v>
       </c>
       <c r="AV4" s="2" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo va vers le poulailler. Le foin sent bon. maman est tout près. Hugo dit les trois noms. Hugo dit les trois noms de la famille. maman sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1825,6 +1859,11 @@
       <c r="AV5" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Le coq, la poule, et le petit. Quel est le petit ?</t>
         </is>
       </c>
     </row>
@@ -1993,6 +2032,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|Oui. Hugo a retenu. Hugo dit les trois noms de la famille. On continue avec maman.</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2179,6 +2223,11 @@
         <v>8</v>
       </c>
       <c r="AV7" s="2" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le coq, le cheval, ou le chien.</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2341,6 +2390,11 @@
         <v>8</v>
       </c>
       <c r="AV8" s="2" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo a choisi le coq. La poule picore. maman montre lentement. Hugo nomme le mâle. Hugo dit les trois noms de la famille. papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2527,6 +2581,11 @@
         <v>8</v>
       </c>
       <c r="AV9" s="2" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le poussin, le poulain, ou le chiot.</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -2689,6 +2748,11 @@
         <v>8</v>
       </c>
       <c r="AV10" s="2" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo rejoint le poussin. Maman est près. Hugo dit les trois noms. Hugo dit les trois noms de la famille. maman dit merci. le poulailler, puis le coq.</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2851,6 +2915,11 @@
         <v>8</v>
       </c>
       <c r="AV11" s="2" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3013,6 +3082,11 @@
         <v>8</v>
       </c>
       <c r="AV12" s="2" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo rejoint le poulain. Un oiseau crie. Hugo nomme le mâle. Hugo dit les trois noms de la famille. maman dit merci. le poulailler, puis le coq.</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3175,6 +3249,11 @@
         <v>8</v>
       </c>
       <c r="AV13" s="2" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3337,6 +3416,11 @@
         <v>8</v>
       </c>
       <c r="AV14" s="2" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo rejoint le chiot. Le soleil est chaud. Hugo nomme la femelle. Hugo dit les trois noms de la famille. maman dit merci. le poulailler, puis le coq.</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3499,6 +3583,11 @@
         <v>8</v>
       </c>
       <c r="AV15" s="2" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3661,6 +3750,11 @@
         <v>8</v>
       </c>
       <c r="AV16" s="2" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo a choisi le cheval. L'herbe est haute. maman montre lentement. Hugo nomme la femelle. Hugo dit les trois noms de la famille. papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3847,6 +3941,11 @@
         <v>8</v>
       </c>
       <c r="AV17" s="2" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le poussin, le poulain, ou le chiot.</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -4009,6 +4108,11 @@
         <v>8</v>
       </c>
       <c r="AV18" s="2" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo rejoint le poussin. Un oiseau crie. Hugo nomme le mâle. Hugo dit les trois noms de la famille. maman dit merci. le poulailler, puis le cheval.</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4171,6 +4275,11 @@
         <v>8</v>
       </c>
       <c r="AV19" s="2" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4333,6 +4442,11 @@
         <v>8</v>
       </c>
       <c r="AV20" s="2" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo rejoint le poulain. Le soleil est chaud. Hugo nomme la femelle. Hugo dit les trois noms de la famille. maman dit merci. le poulailler, puis le cheval.</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4495,6 +4609,11 @@
         <v>8</v>
       </c>
       <c r="AV21" s="2" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4657,6 +4776,11 @@
         <v>8</v>
       </c>
       <c r="AV22" s="2" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo rejoint le chiot. Le poussin est jaune. Hugo nomme le petit. Hugo dit les trois noms de la famille. maman dit merci. le poulailler, puis le cheval.</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4819,6 +4943,11 @@
         <v>8</v>
       </c>
       <c r="AV23" s="2" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -4981,6 +5110,11 @@
         <v>8</v>
       </c>
       <c r="AV24" s="2" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo a choisi le chien. La niche est en bois. maman montre lentement. Hugo nomme le petit. Hugo dit les trois noms de la famille. papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5167,6 +5301,11 @@
         <v>8</v>
       </c>
       <c r="AV25" s="2" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le poussin, le poulain, ou le chiot.</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -5329,6 +5468,11 @@
         <v>8</v>
       </c>
       <c r="AV26" s="2" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo rejoint le poussin. Le soleil est chaud. Hugo nomme la femelle. Hugo dit les trois noms de la famille. maman dit merci. le poulailler, puis le chien.</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5491,6 +5635,11 @@
         <v>8</v>
       </c>
       <c r="AV27" s="2" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5653,6 +5802,11 @@
         <v>8</v>
       </c>
       <c r="AV28" s="2" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo rejoint le poulain. Le poussin est jaune. Hugo nomme le petit. Hugo dit les trois noms de la famille. maman dit merci. le poulailler, puis le chien.</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -5815,6 +5969,11 @@
         <v>8</v>
       </c>
       <c r="AV29" s="2" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -5977,6 +6136,11 @@
         <v>8</v>
       </c>
       <c r="AV30" s="2" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo rejoint le chiot. Le poulain est fin. Hugo répète la famille. Hugo dit les trois noms de la famille. maman dit merci. le poulailler, puis le chien.</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6139,6 +6303,11 @@
         <v>8</v>
       </c>
       <c r="AV31" s="2" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6301,6 +6470,11 @@
         <v>8</v>
       </c>
       <c r="AV32" s="2" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo va vers le pré. Un cheval souffle. maman est tout près. Hugo nomme le mâle. Hugo dit les trois noms de la famille. maman sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6479,6 +6653,11 @@
           <t>question d'écoute, ne change pas le cours</t>
         </is>
       </c>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>narrateur|Le coq, la poule, et le petit. Quel est le petit ?</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -6503,7 +6682,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>Hugo respire. Hugo dit les trois noms de la famille. maman dit : je suis là.</t>
+          <t>Hugo respire. Hugo dit les trois noms de la famille. Je suis là.</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -6645,6 +6824,12 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo respire. Hugo dit les trois noms de la famille.
+maman|Je suis là.</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -6831,6 +7016,11 @@
         <v>8</v>
       </c>
       <c r="AV35" s="2" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le coq, le cheval, ou le chien.</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -6993,6 +7183,11 @@
         <v>8</v>
       </c>
       <c r="AV36" s="2" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo a choisi le coq. Maman est près. maman montre lentement. Hugo nomme la femelle. Hugo dit les trois noms de la famille. papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7179,6 +7374,11 @@
         <v>8</v>
       </c>
       <c r="AV37" s="2" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le poussin, le poulain, ou le chiot.</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -7341,6 +7541,11 @@
         <v>8</v>
       </c>
       <c r="AV38" s="2" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo rejoint le poussin. Un oiseau crie. Hugo dit les trois noms. Hugo dit les trois noms de la famille. maman dit merci. le pré, puis le coq.</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7503,6 +7708,11 @@
         <v>8</v>
       </c>
       <c r="AV39" s="2" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7665,6 +7875,11 @@
         <v>8</v>
       </c>
       <c r="AV40" s="2" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo rejoint le poulain. Le soleil est chaud. Hugo nomme le mâle. Hugo dit les trois noms de la famille. maman dit merci. le pré, puis le coq.</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -7827,6 +8042,11 @@
         <v>8</v>
       </c>
       <c r="AV41" s="2" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -7989,6 +8209,11 @@
         <v>8</v>
       </c>
       <c r="AV42" s="2" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo rejoint le chiot. Le poussin est jaune. Hugo nomme la femelle. Hugo dit les trois noms de la famille. maman dit merci. le pré, puis le coq.</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8151,6 +8376,11 @@
         <v>8</v>
       </c>
       <c r="AV43" s="2" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -8313,6 +8543,11 @@
         <v>8</v>
       </c>
       <c r="AV44" s="2" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo a choisi le cheval. Un oiseau crie. maman montre lentement. Hugo nomme le petit. Hugo dit les trois noms de la famille. papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8499,6 +8734,11 @@
         <v>8</v>
       </c>
       <c r="AV45" s="2" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le poussin, le poulain, ou le chiot.</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -8661,6 +8901,11 @@
         <v>8</v>
       </c>
       <c r="AV46" s="2" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo rejoint le poussin. Le soleil est chaud. Hugo nomme le mâle. Hugo dit les trois noms de la famille. maman dit merci. le pré, puis le cheval.</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -8823,6 +9068,11 @@
         <v>8</v>
       </c>
       <c r="AV47" s="2" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -8985,6 +9235,11 @@
         <v>8</v>
       </c>
       <c r="AV48" s="2" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo rejoint le poulain. Le poussin est jaune. Hugo nomme la femelle. Hugo dit les trois noms de la famille. maman dit merci. le pré, puis le cheval.</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9147,6 +9402,11 @@
         <v>8</v>
       </c>
       <c r="AV49" s="2" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -9309,6 +9569,11 @@
         <v>8</v>
       </c>
       <c r="AV50" s="2" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo rejoint le chiot. Le poulain est fin. Hugo nomme le petit. Hugo dit les trois noms de la famille. maman dit merci. le pré, puis le cheval.</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9471,6 +9736,11 @@
         <v>8</v>
       </c>
       <c r="AV51" s="2" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -9633,6 +9903,11 @@
         <v>8</v>
       </c>
       <c r="AV52" s="2" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo a choisi le chien. Le soleil est chaud. maman montre lentement. Hugo répète la famille. Hugo dit les trois noms de la famille. papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -9819,6 +10094,11 @@
         <v>8</v>
       </c>
       <c r="AV53" s="2" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le poussin, le poulain, ou le chiot.</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -9981,6 +10261,11 @@
         <v>8</v>
       </c>
       <c r="AV54" s="2" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo rejoint le poussin. Le poussin est jaune. Hugo nomme la femelle. Hugo dit les trois noms de la famille. maman dit merci. le pré, puis le chien.</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10143,6 +10428,11 @@
         <v>8</v>
       </c>
       <c r="AV55" s="2" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -10305,6 +10595,11 @@
         <v>8</v>
       </c>
       <c r="AV56" s="2" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo rejoint le poulain. Le poulain est fin. Hugo nomme le petit. Hugo dit les trois noms de la famille. maman dit merci. le pré, puis le chien.</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10467,6 +10762,11 @@
         <v>8</v>
       </c>
       <c r="AV57" s="2" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -10629,6 +10929,11 @@
         <v>8</v>
       </c>
       <c r="AV58" s="2" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo rejoint le chiot. Le chiot dort. Hugo répète la famille. Hugo dit les trois noms de la famille. maman dit merci. le pré, puis le chien.</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -10791,6 +11096,11 @@
         <v>8</v>
       </c>
       <c r="AV59" s="2" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -10953,6 +11263,11 @@
         <v>8</v>
       </c>
       <c r="AV60" s="2" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo va vers la niche. Un chien grogne tout doux. maman est tout près. Hugo nomme la femelle. Hugo dit les trois noms de la famille. maman sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11129,6 +11444,11 @@
       <c r="AV61" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>narrateur|Le coq, la poule, et le petit. Quel est le petit ?</t>
         </is>
       </c>
     </row>
@@ -11297,6 +11617,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>narrateur|C'est juste. Hugo dit les trois noms de la famille. Hugo donne la main à maman.</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -11483,6 +11808,11 @@
         <v>8</v>
       </c>
       <c r="AV63" s="2" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le coq, le cheval, ou le chien.</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -11645,6 +11975,11 @@
         <v>8</v>
       </c>
       <c r="AV64" s="2" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo a choisi le coq. Le poussin est jaune. maman montre lentement. Hugo nomme le petit. Hugo dit les trois noms de la famille. papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -11831,6 +12166,11 @@
         <v>8</v>
       </c>
       <c r="AV65" s="2" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le poussin, le poulain, ou le chiot.</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -11993,6 +12333,11 @@
         <v>8</v>
       </c>
       <c r="AV66" s="2" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo rejoint le poussin. Le soleil est chaud. Hugo dit les trois noms. Hugo dit les trois noms de la famille. maman dit merci. la niche, puis le coq.</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12155,6 +12500,11 @@
         <v>8</v>
       </c>
       <c r="AV67" s="2" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -12317,6 +12667,11 @@
         <v>8</v>
       </c>
       <c r="AV68" s="2" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo rejoint le poulain. Le poussin est jaune. Hugo nomme le mâle. Hugo dit les trois noms de la famille. maman dit merci. la niche, puis le coq.</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -12479,6 +12834,11 @@
         <v>8</v>
       </c>
       <c r="AV69" s="2" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -12641,6 +13001,11 @@
         <v>8</v>
       </c>
       <c r="AV70" s="2" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo rejoint le chiot. Le poulain est fin. Hugo nomme la femelle. Hugo dit les trois noms de la famille. maman dit merci. la niche, puis le coq.</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -12803,6 +13168,11 @@
         <v>8</v>
       </c>
       <c r="AV71" s="2" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -12965,6 +13335,11 @@
         <v>8</v>
       </c>
       <c r="AV72" s="2" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo a choisi le cheval. Le poulain est fin. maman montre lentement. Hugo répète la famille. Hugo dit les trois noms de la famille. papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13151,6 +13526,11 @@
         <v>8</v>
       </c>
       <c r="AV73" s="2" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le poussin, le poulain, ou le chiot.</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -13313,6 +13693,11 @@
         <v>8</v>
       </c>
       <c r="AV74" s="2" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo rejoint le poussin. Le poussin est jaune. Hugo nomme le mâle. Hugo dit les trois noms de la famille. maman dit merci. la niche, puis le cheval.</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -13475,6 +13860,11 @@
         <v>8</v>
       </c>
       <c r="AV75" s="2" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -13637,6 +14027,11 @@
         <v>8</v>
       </c>
       <c r="AV76" s="2" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo rejoint le poulain. Le poulain est fin. Hugo nomme la femelle. Hugo dit les trois noms de la famille. maman dit merci. la niche, puis le cheval.</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -13799,6 +14194,11 @@
         <v>8</v>
       </c>
       <c r="AV77" s="2" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -13961,6 +14361,11 @@
         <v>8</v>
       </c>
       <c r="AV78" s="2" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo rejoint le chiot. Le chiot dort. Hugo nomme le petit. Hugo dit les trois noms de la famille. maman dit merci. la niche, puis le cheval.</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14123,6 +14528,11 @@
         <v>8</v>
       </c>
       <c r="AV79" s="2" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -14285,6 +14695,11 @@
         <v>8</v>
       </c>
       <c r="AV80" s="2" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo a choisi le chien. Le chiot dort. maman montre lentement. Hugo dit les trois noms. Hugo dit les trois noms de la famille. papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -14471,6 +14886,11 @@
         <v>8</v>
       </c>
       <c r="AV81" s="2" t="inlineStr"/>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le poussin, le poulain, ou le chiot.</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -14633,6 +15053,11 @@
         <v>8</v>
       </c>
       <c r="AV82" s="2" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo rejoint le poussin. Le poulain est fin. Hugo nomme la femelle. Hugo dit les trois noms de la famille. maman dit merci. la niche, puis le chien.</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -14795,6 +15220,11 @@
         <v>8</v>
       </c>
       <c r="AV83" s="2" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -14957,6 +15387,11 @@
         <v>8</v>
       </c>
       <c r="AV84" s="2" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo rejoint le poulain. Le chiot dort. Hugo nomme le petit. Hugo dit les trois noms de la famille. maman dit merci. la niche, puis le chien.</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -15119,6 +15554,11 @@
         <v>8</v>
       </c>
       <c r="AV85" s="2" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -15281,6 +15721,11 @@
         <v>8</v>
       </c>
       <c r="AV86" s="2" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo rejoint le chiot. Le foin sent bon. Hugo répète la famille. Hugo dit les trois noms de la famille. maman dit merci. la niche, puis le chien.</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -15443,6 +15888,11 @@
         <v>8</v>
       </c>
       <c r="AV87" s="2" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV87"/>
@@ -15461,7 +15911,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -15478,6 +15928,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/TREE-VIV-005.xlsx
+++ b/stories/arbres/TREE-VIV-005.xlsx
@@ -857,7 +857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW87"/>
+  <dimension ref="A1:AX87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1156,6 +1156,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1325,6 +1330,11 @@
 narrateur|Hugo répète.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1516,6 +1526,7 @@
           <t>narrateur|On peut prendre le poulailler, le pré, ou la niche.</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1683,6 +1694,7 @@
           <t>narrateur|Hugo va vers le poulailler. Le foin sent bon. maman est tout près. Hugo dit les trois noms. Hugo dit les trois noms de la famille. maman sourit.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1866,6 +1878,7 @@
           <t>narrateur|Le coq, la poule, et le petit. Quel est le petit ?</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2037,6 +2050,7 @@
           <t>narrateur|Oui. Hugo a retenu. Hugo dit les trois noms de la famille. On continue avec maman.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2226,6 +2240,11 @@
       <c r="AW7" t="inlineStr">
         <is>
           <t>narrateur|On peut prendre le coq, le cheval, ou le chien.</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
         </is>
       </c>
     </row>
@@ -2395,6 +2414,7 @@
           <t>narrateur|Hugo a choisi le coq. La poule picore. maman montre lentement. Hugo nomme le mâle. Hugo dit les trois noms de la famille. papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2586,6 +2606,7 @@
           <t>narrateur|On peut prendre le poussin, le poulain, ou le chiot.</t>
         </is>
       </c>
+      <c r="AX9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -2753,6 +2774,7 @@
           <t>narrateur|Hugo rejoint le poussin. Maman est près. Hugo dit les trois noms. Hugo dit les trois noms de la famille. maman dit merci. le poulailler, puis le coq.</t>
         </is>
       </c>
+      <c r="AX10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2920,6 +2942,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3087,6 +3110,7 @@
           <t>narrateur|Hugo rejoint le poulain. Un oiseau crie. Hugo nomme le mâle. Hugo dit les trois noms de la famille. maman dit merci. le poulailler, puis le coq.</t>
         </is>
       </c>
+      <c r="AX12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3254,6 +3278,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3421,6 +3446,7 @@
           <t>narrateur|Hugo rejoint le chiot. Le soleil est chaud. Hugo nomme la femelle. Hugo dit les trois noms de la famille. maman dit merci. le poulailler, puis le coq.</t>
         </is>
       </c>
+      <c r="AX14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3588,6 +3614,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3755,6 +3782,7 @@
           <t>narrateur|Hugo a choisi le cheval. L'herbe est haute. maman montre lentement. Hugo nomme la femelle. Hugo dit les trois noms de la famille. papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3946,6 +3974,7 @@
           <t>narrateur|On peut prendre le poussin, le poulain, ou le chiot.</t>
         </is>
       </c>
+      <c r="AX17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -4113,6 +4142,7 @@
           <t>narrateur|Hugo rejoint le poussin. Un oiseau crie. Hugo nomme le mâle. Hugo dit les trois noms de la famille. maman dit merci. le poulailler, puis le cheval.</t>
         </is>
       </c>
+      <c r="AX18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4280,6 +4310,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4447,6 +4478,7 @@
           <t>narrateur|Hugo rejoint le poulain. Le soleil est chaud. Hugo nomme la femelle. Hugo dit les trois noms de la famille. maman dit merci. le poulailler, puis le cheval.</t>
         </is>
       </c>
+      <c r="AX20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4614,6 +4646,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4781,6 +4814,7 @@
           <t>narrateur|Hugo rejoint le chiot. Le poussin est jaune. Hugo nomme le petit. Hugo dit les trois noms de la famille. maman dit merci. le poulailler, puis le cheval.</t>
         </is>
       </c>
+      <c r="AX22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4948,6 +4982,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -5115,6 +5150,11 @@
           <t>narrateur|Hugo a choisi le chien. La niche est en bois. maman montre lentement. Hugo nomme le petit. Hugo dit les trois noms de la famille. papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5306,6 +5346,7 @@
           <t>narrateur|On peut prendre le poussin, le poulain, ou le chiot.</t>
         </is>
       </c>
+      <c r="AX25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -5473,6 +5514,11 @@
           <t>narrateur|Hugo rejoint le poussin. Le soleil est chaud. Hugo nomme la femelle. Hugo dit les trois noms de la famille. maman dit merci. le poulailler, puis le chien.</t>
         </is>
       </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5640,6 +5686,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5807,6 +5854,11 @@
           <t>narrateur|Hugo rejoint le poulain. Le poussin est jaune. Hugo nomme le petit. Hugo dit les trois noms de la famille. maman dit merci. le poulailler, puis le chien.</t>
         </is>
       </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -5974,6 +6026,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -6141,6 +6194,11 @@
           <t>narrateur|Hugo rejoint le chiot. Le poulain est fin. Hugo répète la famille. Hugo dit les trois noms de la famille. maman dit merci. le poulailler, puis le chien.</t>
         </is>
       </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6308,6 +6366,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6475,6 +6534,7 @@
           <t>narrateur|Hugo va vers le pré. Un cheval souffle. maman est tout près. Hugo nomme le mâle. Hugo dit les trois noms de la famille. maman sourit.</t>
         </is>
       </c>
+      <c r="AX32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6658,6 +6718,7 @@
           <t>narrateur|Le coq, la poule, et le petit. Quel est le petit ?</t>
         </is>
       </c>
+      <c r="AX33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -6830,6 +6891,7 @@
 maman|Je suis là.</t>
         </is>
       </c>
+      <c r="AX34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -7019,6 +7081,11 @@
       <c r="AW35" t="inlineStr">
         <is>
           <t>narrateur|On peut prendre le coq, le cheval, ou le chien.</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
         </is>
       </c>
     </row>
@@ -7188,6 +7255,7 @@
           <t>narrateur|Hugo a choisi le coq. Maman est près. maman montre lentement. Hugo nomme la femelle. Hugo dit les trois noms de la famille. papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7379,6 +7447,7 @@
           <t>narrateur|On peut prendre le poussin, le poulain, ou le chiot.</t>
         </is>
       </c>
+      <c r="AX37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -7546,6 +7615,7 @@
           <t>narrateur|Hugo rejoint le poussin. Un oiseau crie. Hugo dit les trois noms. Hugo dit les trois noms de la famille. maman dit merci. le pré, puis le coq.</t>
         </is>
       </c>
+      <c r="AX38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7713,6 +7783,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7880,6 +7951,7 @@
           <t>narrateur|Hugo rejoint le poulain. Le soleil est chaud. Hugo nomme le mâle. Hugo dit les trois noms de la famille. maman dit merci. le pré, puis le coq.</t>
         </is>
       </c>
+      <c r="AX40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -8047,6 +8119,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -8214,6 +8287,7 @@
           <t>narrateur|Hugo rejoint le chiot. Le poussin est jaune. Hugo nomme la femelle. Hugo dit les trois noms de la famille. maman dit merci. le pré, puis le coq.</t>
         </is>
       </c>
+      <c r="AX42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8381,6 +8455,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -8548,6 +8623,7 @@
           <t>narrateur|Hugo a choisi le cheval. Un oiseau crie. maman montre lentement. Hugo nomme le petit. Hugo dit les trois noms de la famille. papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8739,6 +8815,7 @@
           <t>narrateur|On peut prendre le poussin, le poulain, ou le chiot.</t>
         </is>
       </c>
+      <c r="AX45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -8906,6 +8983,7 @@
           <t>narrateur|Hugo rejoint le poussin. Le soleil est chaud. Hugo nomme le mâle. Hugo dit les trois noms de la famille. maman dit merci. le pré, puis le cheval.</t>
         </is>
       </c>
+      <c r="AX46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -9073,6 +9151,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -9240,6 +9319,7 @@
           <t>narrateur|Hugo rejoint le poulain. Le poussin est jaune. Hugo nomme la femelle. Hugo dit les trois noms de la famille. maman dit merci. le pré, puis le cheval.</t>
         </is>
       </c>
+      <c r="AX48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9407,6 +9487,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -9574,6 +9655,7 @@
           <t>narrateur|Hugo rejoint le chiot. Le poulain est fin. Hugo nomme le petit. Hugo dit les trois noms de la famille. maman dit merci. le pré, puis le cheval.</t>
         </is>
       </c>
+      <c r="AX50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9741,6 +9823,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -9908,6 +9991,11 @@
           <t>narrateur|Hugo a choisi le chien. Le soleil est chaud. maman montre lentement. Hugo répète la famille. Hugo dit les trois noms de la famille. papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -10099,6 +10187,7 @@
           <t>narrateur|On peut prendre le poussin, le poulain, ou le chiot.</t>
         </is>
       </c>
+      <c r="AX53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -10266,6 +10355,11 @@
           <t>narrateur|Hugo rejoint le poussin. Le poussin est jaune. Hugo nomme la femelle. Hugo dit les trois noms de la famille. maman dit merci. le pré, puis le chien.</t>
         </is>
       </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10433,6 +10527,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -10600,6 +10695,11 @@
           <t>narrateur|Hugo rejoint le poulain. Le poulain est fin. Hugo nomme le petit. Hugo dit les trois noms de la famille. maman dit merci. le pré, puis le chien.</t>
         </is>
       </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10767,6 +10867,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -10934,6 +11035,11 @@
           <t>narrateur|Hugo rejoint le chiot. Le chiot dort. Hugo répète la famille. Hugo dit les trois noms de la famille. maman dit merci. le pré, puis le chien.</t>
         </is>
       </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -11101,6 +11207,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -11268,6 +11375,11 @@
           <t>narrateur|Hugo va vers la niche. Un chien grogne tout doux. maman est tout près. Hugo nomme la femelle. Hugo dit les trois noms de la famille. maman sourit.</t>
         </is>
       </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11451,6 +11563,7 @@
           <t>narrateur|Le coq, la poule, et le petit. Quel est le petit ?</t>
         </is>
       </c>
+      <c r="AX61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
@@ -11622,6 +11735,7 @@
           <t>narrateur|C'est juste. Hugo dit les trois noms de la famille. Hugo donne la main à maman.</t>
         </is>
       </c>
+      <c r="AX62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -11811,6 +11925,11 @@
       <c r="AW63" t="inlineStr">
         <is>
           <t>narrateur|On peut prendre le coq, le cheval, ou le chien.</t>
+        </is>
+      </c>
+      <c r="AX63" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
         </is>
       </c>
     </row>
@@ -11980,6 +12099,7 @@
           <t>narrateur|Hugo a choisi le coq. Le poussin est jaune. maman montre lentement. Hugo nomme le petit. Hugo dit les trois noms de la famille. papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -12171,6 +12291,7 @@
           <t>narrateur|On peut prendre le poussin, le poulain, ou le chiot.</t>
         </is>
       </c>
+      <c r="AX65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -12338,6 +12459,7 @@
           <t>narrateur|Hugo rejoint le poussin. Le soleil est chaud. Hugo dit les trois noms. Hugo dit les trois noms de la famille. maman dit merci. la niche, puis le coq.</t>
         </is>
       </c>
+      <c r="AX66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12505,6 +12627,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -12672,6 +12795,7 @@
           <t>narrateur|Hugo rejoint le poulain. Le poussin est jaune. Hugo nomme le mâle. Hugo dit les trois noms de la famille. maman dit merci. la niche, puis le coq.</t>
         </is>
       </c>
+      <c r="AX68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -12839,6 +12963,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -13006,6 +13131,7 @@
           <t>narrateur|Hugo rejoint le chiot. Le poulain est fin. Hugo nomme la femelle. Hugo dit les trois noms de la famille. maman dit merci. la niche, puis le coq.</t>
         </is>
       </c>
+      <c r="AX70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -13173,6 +13299,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -13340,6 +13467,7 @@
           <t>narrateur|Hugo a choisi le cheval. Le poulain est fin. maman montre lentement. Hugo répète la famille. Hugo dit les trois noms de la famille. papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13531,6 +13659,7 @@
           <t>narrateur|On peut prendre le poussin, le poulain, ou le chiot.</t>
         </is>
       </c>
+      <c r="AX73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -13698,6 +13827,7 @@
           <t>narrateur|Hugo rejoint le poussin. Le poussin est jaune. Hugo nomme le mâle. Hugo dit les trois noms de la famille. maman dit merci. la niche, puis le cheval.</t>
         </is>
       </c>
+      <c r="AX74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -13865,6 +13995,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -14032,6 +14163,7 @@
           <t>narrateur|Hugo rejoint le poulain. Le poulain est fin. Hugo nomme la femelle. Hugo dit les trois noms de la famille. maman dit merci. la niche, puis le cheval.</t>
         </is>
       </c>
+      <c r="AX76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -14199,6 +14331,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -14366,6 +14499,7 @@
           <t>narrateur|Hugo rejoint le chiot. Le chiot dort. Hugo nomme le petit. Hugo dit les trois noms de la famille. maman dit merci. la niche, puis le cheval.</t>
         </is>
       </c>
+      <c r="AX78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14533,6 +14667,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -14700,6 +14835,11 @@
           <t>narrateur|Hugo a choisi le chien. Le chiot dort. maman montre lentement. Hugo dit les trois noms. Hugo dit les trois noms de la famille. papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX80" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -14891,6 +15031,7 @@
           <t>narrateur|On peut prendre le poussin, le poulain, ou le chiot.</t>
         </is>
       </c>
+      <c r="AX81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -15058,6 +15199,11 @@
           <t>narrateur|Hugo rejoint le poussin. Le poulain est fin. Hugo nomme la femelle. Hugo dit les trois noms de la famille. maman dit merci. la niche, puis le chien.</t>
         </is>
       </c>
+      <c r="AX82" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -15225,6 +15371,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -15392,6 +15539,11 @@
           <t>narrateur|Hugo rejoint le poulain. Le chiot dort. Hugo nomme le petit. Hugo dit les trois noms de la famille. maman dit merci. la niche, puis le chien.</t>
         </is>
       </c>
+      <c r="AX84" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -15559,6 +15711,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -15726,6 +15879,11 @@
           <t>narrateur|Hugo rejoint le chiot. Le foin sent bon. Hugo répète la famille. Hugo dit les trois noms de la famille. maman dit merci. la niche, puis le chien.</t>
         </is>
       </c>
+      <c r="AX86" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -15893,6 +16051,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX87" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV87"/>
@@ -15911,7 +16070,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -15935,6 +16094,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -15949,7 +16122,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -16136,6 +16309,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
